--- a/public/invoices/GS-PHONEBOX-001-V3.0.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V3.0.xlsx
@@ -667,7 +667,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Activation: July 17, 2026</t>
+          <t>Activation: Friday, July 17, 2026</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>(backup July 18, 2026)</t>
+          <t>Venue: Euclid Oval, Lincoln Road Mall</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="12" ht="50" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Single-event programme: fully-painted pink British phone box with interactive call/voucher/photo tech, deployed for a one-day street activation at Lincoln Road Mall, Miami Beach on July 17, 2026 (backup July 18). Light touchup post-Miami; logistical return to NYC handoff destination — no NYC retail activation, no respray/rewrap package.</t>
+          <t>Single-event programme: fully-painted pink British phone box with interactive call/voucher/photo tech, deployed for a one-day street activation at Euclid Oval, Lincoln Road Mall, Miami Beach on Friday, July 17, 2026 (Saturday, July 18 held as a weather contingency). Light touchup post-Miami; logistical return to NYC handoff destination — no NYC retail activation, no respray/rewrap package.</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Portable A-frame signage, branded stanchions, pavement decals for Lincoln Road street activation</t>
+          <t>Portable A-frame signage, branded stanchions, pavement decals for the Euclid Oval street activation</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
@@ -991,7 +991,7 @@
     <row r="36" ht="24" customHeight="1">
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Phase 04a  —  The Activation (Lincoln Road, Miami Beach)</t>
+          <t>Phase 04a  —  The Activation (Euclid Oval, Lincoln Road Mall, Miami Beach)</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
     <row r="40" ht="22" customHeight="1">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Subtotal — The Activation (Lincoln Road)</t>
+          <t>Subtotal — The Activation (Euclid Oval)</t>
         </is>
       </c>
       <c r="D40" s="12" t="n">

--- a/public/invoices/GS-PHONEBOX-001-V3.0.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V3.0.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice GS-PHONEBOX-001 V3.0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V3.0 — Current" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V2.0 — Superseded" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V1.0 — Initial" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -148,17 +150,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -563,6 +560,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00D4AF37"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -586,7 +584,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EXPERIENTIAL FABRICATION &amp; PRODUCTION  ·  PROPOSAL INVOICE</t>
+          <t>EXPERIENTIAL FABRICATION &amp; PRODUCTION  ·  PROPOSAL INVOICE  ·  Version 3.0</t>
         </is>
       </c>
     </row>
@@ -664,7 +662,6 @@
           <t>julian@agvmiami.com</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Activation: Friday, July 17, 2026</t>
@@ -684,527 +681,527 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>V3.0 SCOPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>3.0 SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Single-event programme: fully-painted pink British phone box with interactive call/voucher/photo tech, deployed for a one-day street activation at Euclid Oval, Lincoln Road Mall, Miami Beach on Friday, July 17, 2026 (Saturday, July 18 held as a weather contingency). Light touchup post-Miami; logistical return to NYC handoff destination — no NYC retail activation, no respray/rewrap package.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Phase 01  —  The Phone Box (Painted Finish)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Phone Box Structural Shell</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Custom scenic fabrication, marine-grade paint in Gymshark Pink, two-piece modular construction</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="9" t="n">
         <v>14500</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>4-Sided Illuminated Lightbox Signage</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>LED-backlit translucent face panels on all four sides; weatherproof housing</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>6800</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Glass &amp; Semi-Transparent Vinyl Panels</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Tempered glass on front door + sides with custom-printed semi-transparent privacy vinyl</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="9" t="n">
         <v>2900</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Pink Painted Interior Finish (V3.0)</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Fully-painted four-wall pink interior — replaces vinyl-lined interior for durability and finish quality</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>3200</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Concealed Sliding Prize Door</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Motorised, colour-matched, no visible handle on public face</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="9" t="n">
         <v>3400</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Interior Finishes</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Aluminium chequer-plate flooring, dome light, guest seat, branded analogue phone</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>2750</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Engineering, Structural Calcs &amp; Shop Drawings</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Wind-load, ballast plan, electrical schematics, CAD shop drawings, venue-compliance package</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="9" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Subtotal — The Phone Box</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="11" t="n">
         <v>37550</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Phase 02  —  Interactive Tech + Content Capture</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Pre-Recorded Call-Response (IVR) System</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Multi-branch scripting, licensed voice talent, keypad mapping, redundant win/lose logic, QA</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Live Call / Walkie-Talkie Relay</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Dual-mode encrypted relay, backup uplink, on-site producer headset, external broadcast</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="9" t="n">
         <v>2900</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Ceiling Dual Camera System</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Two 4K video+audio cameras, cloud storage, live-preview monitoring, disclosure signage</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="9" t="n">
         <v>4500</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Selfie &amp; Belfie Mobile Mounts</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Two pink wall-mounted holders with motion-triggered ring-light inserts, dual-height</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="9" t="n">
         <v>1800</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Thermal Voucher Printer &amp; Shelf Mount</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Dual-speed thermal ticket printer, pink wrap, redundant roll inventory, firmware</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="9" t="n">
         <v>2800</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Content Capture &amp; Media Handoff Platform</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Cloud workspace, colour-corrected proxies, organised file-naming, 48-hour handoff</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="9" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Subtotal — Interactive Tech + Content Capture</t>
         </is>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="11" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Phase 03  —  Branding, Signage &amp; Consumables</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Disclosure &amp; Wayfinding Signage</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Camera-disclosure sign, queue management decals, brand lockup callouts in brand palette</t>
         </is>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="9" t="n">
         <v>950</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Venue Dressing Kit</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Portable A-frame signage, branded stanchions, pavement decals for the Euclid Oval street activation</t>
         </is>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D33" s="9" t="n">
         <v>1750</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Daily Consumables &amp; Spares Kit</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Voucher paper rolls, cleaning supplies, sanitisation wipes, touch-up paint, vinyl repair, pink gaffer</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="9" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Subtotal — Branding, Signage &amp; Consumables</t>
         </is>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D35" s="11" t="n">
         <v>5200</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Phase 04a  —  The Activation (Euclid Oval, Lincoln Road Mall, Miami Beach)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Inbound Logistics &amp; Install</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Truck, rigging hardware, 3-person install crew, permit-window supervisor, 4–6 hr install window</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="9" t="n">
         <v>5800</v>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>On-Site Technicians</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Dedicated lead technician plus rotating second tech for rush windows and breaks</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="9" t="n">
         <v>2800</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Same-Day Strike &amp; Outbound Freight</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>Complete de-installation, module breakdown, crated outbound freight, full site restoration</t>
         </is>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="9" t="n">
         <v>3300</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Subtotal — The Activation (Euclid Oval)</t>
         </is>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D40" s="11" t="n">
         <v>11900</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Phase 04b  —  Logistics to NYC (Asset Transfer Only)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Climate-Controlled Warehouse Hold</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Secure climate-controlled storage at the AGV Miami NYC staging facility between Miami strike and NYC handoff</t>
         </is>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="9" t="n">
         <v>2400</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Inter-City Freight (Climate-Controlled Truck)</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>Miami → AGV Miami NYC staging facility with real-time GPS tracking, two-driver rotation, handoff documentation</t>
         </is>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="9" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Light Touchup After First Activation (V3 — new line)</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>Single light cosmetic touchup pass after Miami activation: scuff/scratch repair, paint colour-match, lightbox edge cleanup, IVR/camera/printer functional re-test</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="9" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Final Delivery to NYC Handoff Destination</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>Climate-controlled final-mile delivery from AGV Miami NYC staging to client's designated NYC handoff address. Asset transfer only — no installation, commissioning, or activation.</t>
         </is>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="9" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Subtotal — Logistics to NYC</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="11" t="n">
         <v>12900</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Phase 05  —  Project Management &amp; Client Services</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Project Management Fee</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>Dedicated senior producer, weekly status reporting, milestone tracking, Change Order administration, vendor / venue liaison, COI + insurance coordination, post-event reconciliation</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="9" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Subtotal — Project Management</t>
         </is>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D49" s="11" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>Gross Production Investment</t>
         </is>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D51" s="13" t="n">
         <v>100150</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>Less: Preferred Partner Credit</t>
         </is>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="15" t="n">
         <v>-5000</v>
       </c>
     </row>
     <row r="53" ht="32" customHeight="1">
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>NET V3.0 PRODUCTION INVESTMENT</t>
         </is>
       </c>
-      <c r="D53" s="18" t="n">
+      <c r="D53" s="17" t="n">
         <v>95150</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>PAYMENT TERMS</t>
         </is>
       </c>
     </row>
     <row r="56" ht="70" customHeight="1">
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>60% deposit ($57,090) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($38,060) due five (5) business days prior to first activation installation (i.e., on or before July 10, 2026). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V3.0 on all remittances.</t>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>60% deposit ($57,090) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($38,060) due five (5) business days prior to first activation installation (on or before Friday, July 10, 2026). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V3.0 on all remittances.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="B58" s="19" t="inlineStr">
+      <c r="B58" s="18" t="inlineStr">
         <is>
           <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  julian@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V3.0 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
         </is>
@@ -1237,4 +1234,1419 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000C2A8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:D66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AGV MIAMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXPERIENTIAL FABRICATION &amp; PRODUCTION  ·  PROPOSAL INVOICE  ·  Version 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCER</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Gymshark Ltd.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>GS-PHONEBOX-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1440 Church St</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Attn: Authorized Billing Contact</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Version 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Bohemia, NY 11716</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>c/o Ominto Studio</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Issue Date: April 29, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>julian@agvmiami.com</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Event 01 (Miami): June 27, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>info@agoravisuals.com</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Event 02 (NYC Bond St): July 9 – Aug 6, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2.0 SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Two-event sequence. Event 01 — Miami: Lincoln Road Mall street activation on Saturday, June 27, 2026 (AGV Miami recommended Euclid Oval, 1100 block). Event 02 — New York: in-store fixture at Gymshark Bond St, delivered by July 9, 2026 to anchor the July 11 product launch and a 4-week in-store run through August 6, 2026. Inter-city respray/rewrap to NYC palette between events. [Superseded by V3.0 — included for reference only.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Phase 01  —  The Phone Box</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Phone Box Structural Shell</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Custom scenic fabrication, marine-grade paint, two-piece modular</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>4-Sided Illuminated Lightbox Signage</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>LED-backlit translucent face panels on all four sides</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Glass &amp; Semi-Transparent Vinyl Panels</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Tempered glass on front door + sides</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Pink Vinyl Interior Lining</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Four-wall pink vinyl wrap with 'bum mirror' messaging</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Concealed Sliding Prize Door</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Motorised, colour-matched</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Interior Finishes</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Chequer plate floor, dome light, seat, analogue phone</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Engineering, Structural Calcs &amp; Shop Drawings</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Wind-load, ballast, electrical, CAD</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — The Phone Box</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>37550</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Phase 02  —  Interactive Tech + Content Capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Pre-Recorded Call-Response (IVR) System</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Multi-branch scripting, licensed voice, QA</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Live Call / Walkie-Talkie Relay</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Dual-mode encrypted relay, backup uplink, producer headset</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Ceiling Dual Camera System</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Two 4K cameras, cloud storage, live-preview, disclosure signage</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Selfie &amp; Belfie Mobile Mounts</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Motion-triggered ring-light inserts, dual-height</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Thermal Voucher Printer &amp; Shelf Mount</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Dual-speed thermal printer, pink wrap, redundant roll inventory</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Content Capture &amp; Media Handoff Platform</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Cloud workspace, proxies, 48-hour handoff</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Interactive Tech + Content Capture</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Phase 03  —  Branding, Signage &amp; Consumables</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Disclosure &amp; Wayfinding Signage</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Camera-disclosure, queue management decals, brand lockup callouts</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Venue Dressing Kit</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>A-frame signage, branded stanchions, pavement decals</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Daily Consumables &amp; Spares Kit</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Voucher rolls, cleaning, spares, gaffer</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Branding, Signage &amp; Consumables</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04a  —  Event 01: Miami Lincoln Road Street Activation</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Inbound Logistics &amp; Install (Miami)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>3-person install crew, permit-window supervisor, 4–6 hr install window</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>On-Site Technicians (Miami)</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Lead technician + rotating second tech for rush windows</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Same-Day Strike &amp; Outbound Freight (Miami)</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>De-installation, module breakdown, crated outbound freight</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Event 01 Miami</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04b  —  Inter-City Respray/Rewrap to NYC Palette</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Climate-Controlled Warehouse Hold (10 days)</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Secure climate-controlled storage between Miami strike and NYC delivery</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Inter-City Freight (Miami → NYC, climate truck)</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Dedicated climate truck with two-driver rotation, GPS tracking</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Exterior Vinyl Refresh (NYC Reskin)</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Removal of Miami exterior vinyl + NYC-specific campaign wrap</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Interior Vinyl Refresh (NYC Reskin)</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Removal of Miami interior vinyl + NYC product-launch creative</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Lightbox Graphic Refresh (NYC Reskin)</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Reprint and reinstallation of four lightbox faces with NYC creative</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>NYC Site Re-Survey &amp; Local Permit Coordination</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>On-the-ground survey, permit liaison, COI issuance, site readiness sign-off</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Pre-Deployment QC &amp; Refinishing</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Reassembly inspection, touch-up paint, electrical recheck, system bench-test</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Respray Package</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04c  —  Event 02: NYC Bond St In-Store Activation</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Inbound Logistics &amp; Install (NYC)</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>3-person install crew, permit-window supervisor</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>On-Site Technicians (NYC)</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Lead technician + rotating second tech</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Strike &amp; Outbound Freight (NYC)</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>End-of-launch de-installation and return freight</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Event 02 NYC</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Phase 05  —  Project Management &amp; Client Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Project Management Fee</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Dedicated senior producer, weekly status, milestone tracking, COI + insurance coordination</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Project Management</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Gross Production Investment</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>124150</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Less: Preferred Partner Credit</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="n">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>NET V2.0 PRODUCTION INVESTMENT</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>119150</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>PAYMENT TERMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="70" customHeight="1">
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>60% deposit ($71,490) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($47,660) due five (5) business days prior to first activation installation (five (5) business days prior to Event 01 install). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V2.0 on all remittances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  julian@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V2.0 — superseded by V3.0 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="008A8A95"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:D54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AGV MIAMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXPERIENTIAL FABRICATION &amp; PRODUCTION  ·  PROPOSAL INVOICE  ·  Version 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCER</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Gymshark Ltd.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>GS-PHONEBOX-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1440 Church St</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Attn: Authorized Billing Contact</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Version 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Bohemia, NY 11716</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>c/o Ominto Studio</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Issue Date: April 17, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>julian@agvmiami.com</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Option 03: Miami Jun 27, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>info@agoravisuals.com</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>→ NYC Jul 11, 2026 (with reskin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1.0 SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Initial issuance: three execution options against a $120,000 overall budget. Option 01 NYC-only; Option 02 Miami-only; Option 03 dual-city (Miami first → NYC second) with full inter-city reskin package. Twelve recommended venues across both cities. The figures below itemize the recommended Option 03 dual-city configuration ($98,500 production target). [Superseded by V2.0 and V3.0 — included for reference only.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Phase 01  —  The Phone Box</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Phone Box Structural Shell</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Custom scenic fabrication, marine-grade paint, two-piece modular</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>4-Sided Illuminated Lightbox Signage</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>LED-backlit translucent face panels on all four sides</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Glass &amp; Semi-Transparent Vinyl Panels</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Tempered glass on front door + sides</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Pink Vinyl Interior Lining</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Four-wall pink vinyl wrap with 'bum mirror' messaging</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Concealed Sliding Prize Door</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Motorised, colour-matched</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Interior Finishes</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Chequer plate floor, dome light, seat, analogue phone</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — The Phone Box</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>33550</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Phase 02  —  Interactive Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Pre-Recorded Call-Response (IVR) System</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Scripting, voice, keypad logic</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Live Call / Walkie-Talkie Relay</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Social producer handoff</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Ceiling Dual Camera System</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Video+audio, cloud storage, disclosure sign</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Thermal Voucher Printer &amp; Shelf Mount</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Wrapped, shelf aligned to sliding door</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Selfie &amp; Belfie Mobile Mounts</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Colour-matched, dual-height</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Interactive Tech</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Phase 03  —  Branding &amp; Packaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Custom Product Boxes (200 units)</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Yellow-pages inspired, 300×200×70 mm</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Disclosure &amp; Wayfinding Signage</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Camera disclosure, queue management decals</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Venue Dressing Kit</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>A-frames, stanchions, pavement decals</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Branding &amp; Packaging</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04  —  Logistics, Install &amp; Strike (Per Activation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Inbound Logistics &amp; Install — Miami</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Truck, rigging, install crew, electrical hookup</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>On-Site Technician — Miami</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Single technician across operating window</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Same-Day Strike &amp; Outbound Freight — Miami</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>De-installation, module breakdown, freight</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Inbound Logistics &amp; Install — NYC</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Truck, rigging, install crew, electrical hookup</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>On-Site Technician — NYC</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Single technician across operating window</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Same-Day Strike &amp; Outbound Freight — NYC</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>De-installation, module breakdown, freight</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Two-City Logistics</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04 Add-On  —  Inter-City Rewrap (Option 03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Inter-City Rewrap &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Warehouse hold, vinyl refresh, Miami↔NYC truck</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Inter-City Rewrap</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>V1.0 Note  —  Other Programme Elements (Bundled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Programme Bundle (V1.0 reference)</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>V1.0 published a $98,500 dual-city production target that included additional logistics, contingency, and venue-specific finishing not yet itemized at issuance. The line items above ($77,650) plus this bundled allowance ($20,850) reconcile to the published $98,500 V1.0 figure. Subsequent versions broke out these items individually (engineering, content capture, project management, retail/respray scope changes).</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>20850</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Bundled Allowance</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>20850</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>V1.0 Production Investment (Option 03 Dual-City)</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>98500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>PAYMENT TERMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="70" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>60% deposit ($59,100) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($39,400) due five (5) business days prior to first activation installation (three (3) business days prior to first activation). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V1.0 on all remittances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  julian@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V1.0 — superseded by V2.0 and V3.0 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/invoices/GS-PHONEBOX-001-V3.0.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V3.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V3.0 — Current" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V3.0 — Issued" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -657,7 +657,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>julian@agvmiami.com</t>
+          <t>jclarkson@agvmiami.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="58" ht="32" customHeight="1">
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  julian@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V3.0 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
+          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V3.0 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
         </is>
       </c>
     </row>

--- a/public/invoices/GS-PHONEBOX-001-V3.0.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V3.0.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Venue: Euclid Oval, Lincoln Road Mall</t>
+          <t>Venue: Lincoln Road Mall</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <row r="12" ht="70" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Single-event programme: fully-painted pink British phone box with interactive call/voucher/photo tech, deployed for a one-day street activation at Euclid Oval, Lincoln Road Mall, Miami Beach on Friday, July 17, 2026 (Saturday, July 18 held as a weather contingency). Light touchup post-Miami; logistical return to NYC handoff destination — no NYC retail activation, no respray/rewrap package.</t>
+          <t>Single-event programme: fully-painted pink British phone box with interactive call/voucher/photo tech, deployed for a one-day street activation at Lincoln Road Mall, Miami Beach on Friday, July 17, 2026 (Saturday, July 18 held as a weather contingency). Light touchup post-Miami; logistical return to NYC handoff destination — no NYC retail activation, no respray/rewrap package.</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Portable A-frame signage, branded stanchions, pavement decals for the Euclid Oval street activation</t>
+          <t>Portable A-frame signage, branded stanchions, pavement decals for the Lincoln Road Mall street activation</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
@@ -986,7 +986,7 @@
     <row r="36" ht="24" customHeight="1">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Phase 04a  —  The Activation (Euclid Oval, Lincoln Road Mall, Miami Beach)</t>
+          <t>Phase 04a  —  The Activation (Lincoln Road Mall, Miami Beach)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <row r="40" ht="22" customHeight="1">
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Subtotal — The Activation (Euclid Oval)</t>
+          <t>Subtotal — The Activation (Lincoln Road Mall)</t>
         </is>
       </c>
       <c r="D40" s="11" t="n">
